--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -698,7 +698,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -898,26 +898,26 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>-100</v>
       </c>
       <c r="I15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="14">
         <v>-100</v>
@@ -937,101 +937,101 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
+        <v>2</v>
+      </c>
+      <c r="D16" s="15">
         <v>3</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="E16" s="14">
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
+        <v>9</v>
+      </c>
+      <c r="G16" s="15">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>125</v>
+      </c>
+      <c r="I16" s="15">
+        <v>12</v>
+      </c>
+      <c r="J16" s="15">
         <v>6</v>
       </c>
-      <c r="G16" s="15">
-        <v>2</v>
-      </c>
-      <c r="H16" s="14">
-        <v>200</v>
-      </c>
-      <c r="I16" s="15">
-        <v>8</v>
-      </c>
-      <c r="J16" s="15">
-        <v>3</v>
-      </c>
       <c r="K16" s="14">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="L16" s="14">
-        <v>-46.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="14">
-        <v>-27.272727272727</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N16" s="14">
-        <v>-89.041095890411</v>
+        <v>-84.810126582278</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="15">
+        <v>2</v>
       </c>
       <c r="D17" s="15">
         <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G17" s="15">
         <v>10</v>
       </c>
       <c r="H17" s="14">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="I17" s="15">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J17" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K17" s="14">
-        <v>-16.666666666666</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L17" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M17" s="14">
-        <v>25</v>
+        <v>18.181818181818</v>
       </c>
       <c r="N17" s="14">
-        <v>-67.741935483871</v>
+        <v>-64.864864864864</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>0</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H18" s="14">
         <v>-33.333333333333</v>
@@ -1046,13 +1046,13 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>-23.076923076923</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-16.666666666666</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.424242424242</v>
+        <v>-93.377483443708</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F19" s="15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G19" s="15">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H19" s="14">
         <v>0</v>
       </c>
       <c r="I19" s="15">
+        <v>35</v>
+      </c>
+      <c r="J19" s="15">
         <v>29</v>
       </c>
-      <c r="J19" s="15">
-        <v>26</v>
-      </c>
       <c r="K19" s="14">
-        <v>11.538461538461</v>
+        <v>20.689655172413</v>
       </c>
       <c r="L19" s="14">
-        <v>-44.230769230769</v>
+        <v>-47.761194029850</v>
       </c>
       <c r="M19" s="14">
-        <v>-25.641025641025</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N19" s="14">
-        <v>-52.459016393442</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>10</v>
+      </c>
+      <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="E20" s="14">
+        <v>400</v>
+      </c>
+      <c r="F20" s="15">
+        <v>18</v>
+      </c>
+      <c r="G20" s="15">
+        <v>4</v>
+      </c>
+      <c r="H20" s="14">
+        <v>350</v>
+      </c>
+      <c r="I20" s="15">
+        <v>27</v>
+      </c>
+      <c r="J20" s="15">
         <v>6</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>500</v>
-      </c>
-      <c r="F20" s="15">
-        <v>13</v>
-      </c>
-      <c r="G20" s="15">
-        <v>3</v>
-      </c>
-      <c r="H20" s="14">
-        <v>333.333333333333</v>
-      </c>
-      <c r="I20" s="15">
-        <v>16</v>
-      </c>
-      <c r="J20" s="15">
-        <v>4</v>
-      </c>
       <c r="K20" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L20" s="14">
-        <v>-52.941176470588</v>
+        <v>-32.5</v>
       </c>
       <c r="M20" s="14">
-        <v>-20</v>
+        <v>28.571428571428</v>
       </c>
       <c r="N20" s="14">
-        <v>-92.792792792792</v>
+        <v>-89.615384615384</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>7.142857142857</v>
+        <v>81.818181818181</v>
       </c>
       <c r="F21" s="17">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H21" s="18">
-        <v>12.244897959183</v>
+        <v>25.531914893617</v>
       </c>
       <c r="I21" s="17">
+        <v>97</v>
+      </c>
+      <c r="J21" s="17">
         <v>73</v>
       </c>
-      <c r="J21" s="17">
-        <v>62</v>
-      </c>
       <c r="K21" s="18">
-        <v>17.741935483871</v>
+        <v>32.876712328767</v>
       </c>
       <c r="L21" s="18">
-        <v>-40.163934426229</v>
+        <v>-34.459459459459</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.888888888888</v>
+        <v>-7.619047619047</v>
       </c>
       <c r="N21" s="18">
-        <v>-86.095238095238</v>
+        <v>-83.913764510779</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,32 +1185,32 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="14">
+        <v>0</v>
       </c>
       <c r="I22" s="15">
         <v>1</v>
       </c>
-      <c r="J22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="13" t="s">
-        <v>21</v>
+      <c r="J22" s="15">
+        <v>1</v>
+      </c>
+      <c r="K22" s="14">
+        <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M22" s="14">
         <v>0</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E24" s="14">
-        <v>-63.636363636363</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="G24" s="15">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="H24" s="14">
-        <v>-50.833333333333</v>
+        <v>-50</v>
       </c>
       <c r="I24" s="15">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J24" s="15">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="K24" s="14">
-        <v>-43.506493506493</v>
+        <v>-42.011834319526</v>
       </c>
       <c r="L24" s="14">
-        <v>-46.296296296296</v>
+        <v>-50</v>
       </c>
       <c r="M24" s="14">
-        <v>-38.297872340425</v>
+        <v>-40.243902439024</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D25" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E25" s="14">
-        <v>-71.428571428571</v>
+        <v>-30</v>
       </c>
       <c r="F25" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G25" s="15">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H25" s="14">
-        <v>-68.333333333333</v>
+        <v>-61.818181818181</v>
       </c>
       <c r="I25" s="15">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J25" s="15">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K25" s="14">
-        <v>-66.265060240963</v>
+        <v>-63.440860215053</v>
       </c>
       <c r="L25" s="14">
-        <v>-73.831775700934</v>
+        <v>-73.015873015873</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
         <v>26</v>
       </c>
       <c r="G26" s="15">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H26" s="14">
-        <v>-3.703703703703</v>
+        <v>4</v>
       </c>
       <c r="I26" s="15">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J26" s="15">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K26" s="14">
-        <v>-12.195121951219</v>
+        <v>-2.222222222222</v>
       </c>
       <c r="L26" s="14">
-        <v>2.857142857142</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M26" s="14">
-        <v>-16.279069767441</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,26 +1390,26 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>-100</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="14">
         <v>-100</v>
@@ -1432,7 +1432,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="14">
         <v>-100</v>
@@ -1441,22 +1441,22 @@
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I28" s="15">
         <v>2</v>
       </c>
       <c r="J28" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,8 +1560,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="15">
+        <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1569,8 +1569,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="15">
+        <v>3</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -898,11 +898,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
         <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="I16" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16" s="14">
-        <v>100</v>
+        <v>85.714285714285</v>
       </c>
       <c r="L16" s="14">
-        <v>-25</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="M16" s="14">
-        <v>-14.285714285714</v>
+        <v>-18.75</v>
       </c>
       <c r="N16" s="14">
-        <v>-84.810126582278</v>
+        <v>-85.393258426966</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G17" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H17" s="14">
-        <v>-30</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I17" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J17" s="15">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K17" s="14">
-        <v>-7.142857142857</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L17" s="14">
-        <v>30</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M17" s="14">
-        <v>18.181818181818</v>
+        <v>23.076923076923</v>
       </c>
       <c r="N17" s="14">
-        <v>-64.864864864864</v>
+        <v>-63.636363636363</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="15">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
+        <v>2</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="I18" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J18" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K18" s="14">
-        <v>-33.333333333333</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="L18" s="14">
-        <v>-33.333333333333</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M18" s="14">
-        <v>-41.176470588235</v>
+        <v>-45</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.377483443708</v>
+        <v>-93.785310734463</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1063,37 +1063,37 @@
         <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
         <v>19</v>
       </c>
       <c r="G19" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="I19" s="15">
+        <v>41</v>
+      </c>
+      <c r="J19" s="15">
         <v>35</v>
       </c>
-      <c r="J19" s="15">
-        <v>29</v>
-      </c>
       <c r="K19" s="14">
-        <v>20.689655172413</v>
+        <v>17.142857142857</v>
       </c>
       <c r="L19" s="14">
-        <v>-47.761194029850</v>
+        <v>-43.055555555555</v>
       </c>
       <c r="M19" s="14">
-        <v>-16.666666666666</v>
+        <v>-10.869565217391</v>
       </c>
       <c r="N19" s="14">
-        <v>-50</v>
+        <v>-50.602409638554</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
         <v>400</v>
       </c>
       <c r="F20" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="I20" s="15">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K20" s="14">
-        <v>350</v>
+        <v>357.142857142857</v>
       </c>
       <c r="L20" s="14">
-        <v>-32.5</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="M20" s="14">
-        <v>28.571428571428</v>
+        <v>23.076923076923</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.615384615384</v>
+        <v>-89.261744966442</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>81.818181818181</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G21" s="17">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="H21" s="18">
-        <v>25.531914893617</v>
+        <v>14.545454545454</v>
       </c>
       <c r="I21" s="17">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="J21" s="17">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="K21" s="18">
-        <v>32.876712328767</v>
+        <v>28.409090909090</v>
       </c>
       <c r="L21" s="18">
-        <v>-34.459459459459</v>
+        <v>-30.674846625766</v>
       </c>
       <c r="M21" s="18">
-        <v>-7.619047619047</v>
+        <v>-6.611570247933</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.913764510779</v>
+        <v>-83.787661406025</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,11 +1185,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
         <v>1</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M22" s="14">
         <v>0</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>-13.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G24" s="15">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="H24" s="14">
-        <v>-50</v>
+        <v>-53.535353535353</v>
       </c>
       <c r="I24" s="15">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="J24" s="15">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="K24" s="14">
-        <v>-42.011834319526</v>
+        <v>-41.450777202072</v>
       </c>
       <c r="L24" s="14">
-        <v>-50</v>
+        <v>-49.099099099099</v>
       </c>
       <c r="M24" s="14">
-        <v>-40.243902439024</v>
+        <v>-38.918918918918</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E25" s="14">
-        <v>-30</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="15">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G25" s="15">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H25" s="14">
-        <v>-61.818181818181</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I25" s="15">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J25" s="15">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="K25" s="14">
-        <v>-63.440860215053</v>
+        <v>-65.740740740740</v>
       </c>
       <c r="L25" s="14">
-        <v>-73.015873015873</v>
+        <v>-73.943661971831</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>-20</v>
       </c>
       <c r="F26" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G26" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H26" s="14">
-        <v>4</v>
+        <v>7.407407407407</v>
       </c>
       <c r="I26" s="15">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J26" s="15">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K26" s="14">
-        <v>-2.222222222222</v>
+        <v>-5.454545454545</v>
       </c>
       <c r="L26" s="14">
-        <v>4.761904761904</v>
+        <v>10.638297872340</v>
       </c>
       <c r="M26" s="14">
-        <v>-10.204081632653</v>
+        <v>-1.886792452830</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="15">
         <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="I28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="15">
         <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="14">
-        <v>-81.818181818181</v>
+        <v>-75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -898,17 +898,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -917,7 +917,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="14">
         <v>-100</v>
@@ -925,8 +925,8 @@
       <c r="L15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+      <c r="M15" s="14">
+        <v>-100</v>
       </c>
       <c r="N15" s="14">
         <v>-100</v>
@@ -940,37 +940,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>100</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J16" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K16" s="14">
-        <v>85.714285714285</v>
+        <v>55.555555555555</v>
       </c>
       <c r="L16" s="14">
-        <v>-23.529411764705</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M16" s="14">
-        <v>-18.75</v>
+        <v>-12.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-85.393258426966</v>
+        <v>-87.037037037037</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,37 +981,37 @@
         <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-40</v>
+        <v>50</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>-16.666666666666</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I17" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J17" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K17" s="14">
-        <v>-15.789473684210</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L17" s="14">
-        <v>23.076923076923</v>
+        <v>5.882352941176</v>
       </c>
       <c r="M17" s="14">
-        <v>23.076923076923</v>
+        <v>12.5</v>
       </c>
       <c r="N17" s="14">
-        <v>-63.636363636363</v>
+        <v>-60.869565217391</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1022,37 +1022,37 @@
         <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
+        <v>0</v>
+      </c>
+      <c r="F18" s="15">
+        <v>3</v>
+      </c>
+      <c r="G18" s="15">
+        <v>4</v>
+      </c>
+      <c r="H18" s="14">
+        <v>-25</v>
+      </c>
+      <c r="I18" s="15">
+        <v>12</v>
+      </c>
+      <c r="J18" s="15">
+        <v>18</v>
+      </c>
+      <c r="K18" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L18" s="14">
+        <v>-40</v>
+      </c>
+      <c r="M18" s="14">
         <v>-50</v>
       </c>
-      <c r="F18" s="15">
-        <v>4</v>
-      </c>
-      <c r="G18" s="15">
-        <v>10</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-60</v>
-      </c>
-      <c r="I18" s="15">
-        <v>11</v>
-      </c>
-      <c r="J18" s="15">
-        <v>17</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-35.294117647058</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-38.888888888888</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-45</v>
-      </c>
       <c r="N18" s="14">
-        <v>-93.785310734463</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F19" s="15">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G19" s="15">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H19" s="14">
-        <v>-17.391304347826</v>
+        <v>-12.5</v>
       </c>
       <c r="I19" s="15">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="J19" s="15">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="K19" s="14">
-        <v>17.142857142857</v>
+        <v>6.25</v>
       </c>
       <c r="L19" s="14">
-        <v>-43.055555555555</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="M19" s="14">
-        <v>-10.869565217391</v>
+        <v>10.869565217391</v>
       </c>
       <c r="N19" s="14">
-        <v>-50.602409638554</v>
+        <v>-45.744680851063</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" s="15">
         <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F20" s="15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G20" s="15">
         <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="I20" s="15">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>357.142857142857</v>
+        <v>350</v>
       </c>
       <c r="L20" s="14">
-        <v>-25.581395348837</v>
+        <v>-20</v>
       </c>
       <c r="M20" s="14">
-        <v>23.076923076923</v>
+        <v>38.461538461538</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.261744966442</v>
+        <v>-89.534883720930</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>6.666666666666</v>
+        <v>-5</v>
       </c>
       <c r="F21" s="17">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H21" s="18">
-        <v>14.545454545454</v>
+        <v>18.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="J21" s="17">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="K21" s="18">
-        <v>28.409090909090</v>
+        <v>21.296296296296</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.674846625766</v>
+        <v>-26.815642458100</v>
       </c>
       <c r="M21" s="18">
-        <v>-6.611570247933</v>
+        <v>1.550387596899</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.787661406025</v>
+        <v>-83.417721518987</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,14 +1191,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>1</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E24" s="14">
-        <v>-33.333333333333</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="F24" s="15">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G24" s="15">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H24" s="14">
-        <v>-53.535353535353</v>
+        <v>-43.010752688172</v>
       </c>
       <c r="I24" s="15">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="J24" s="15">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="K24" s="14">
-        <v>-41.450777202072</v>
+        <v>-41.121495327102</v>
       </c>
       <c r="L24" s="14">
-        <v>-49.099099099099</v>
+        <v>-46.382978723404</v>
       </c>
       <c r="M24" s="14">
-        <v>-38.918918918918</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>-80</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F25" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G25" s="15">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H25" s="14">
-        <v>-69.230769230769</v>
+        <v>-62.5</v>
       </c>
       <c r="I25" s="15">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J25" s="15">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="K25" s="14">
-        <v>-65.740740740740</v>
+        <v>-64.957264957265</v>
       </c>
       <c r="L25" s="14">
-        <v>-73.943661971831</v>
+        <v>-72.297297297297</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>-20</v>
+        <v>80</v>
       </c>
       <c r="F26" s="15">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G26" s="15">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H26" s="14">
-        <v>7.407407407407</v>
+        <v>37.5</v>
       </c>
       <c r="I26" s="15">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J26" s="15">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K26" s="14">
-        <v>-5.454545454545</v>
+        <v>1.666666666666</v>
       </c>
       <c r="L26" s="14">
-        <v>10.638297872340</v>
+        <v>7.017543859649</v>
       </c>
       <c r="M26" s="14">
-        <v>-1.886792452830</v>
+        <v>7.017543859649</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,17 +1390,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>2</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1409,7 +1409,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="14">
         <v>-100</v>
@@ -1428,14 +1428,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>1</v>
@@ -1450,13 +1450,13 @@
         <v>3</v>
       </c>
       <c r="J28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="14">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L28" s="14">
-        <v>-75</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,8 +1560,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>3</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -898,11 +898,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -936,23 +936,23 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
-      </c>
-      <c r="D16" s="15">
-        <v>2</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-50</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
         <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="15">
         <v>14</v>
@@ -967,51 +967,51 @@
         <v>-26.315789473684</v>
       </c>
       <c r="M16" s="14">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.037037037037</v>
+        <v>-88.034188034188</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>3</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H17" s="14">
-        <v>-27.272727272727</v>
+        <v>-30</v>
       </c>
       <c r="I17" s="15">
         <v>18</v>
       </c>
       <c r="J17" s="15">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K17" s="14">
-        <v>-14.285714285714</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L17" s="14">
-        <v>5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="M17" s="14">
         <v>12.5</v>
       </c>
       <c r="N17" s="14">
-        <v>-60.869565217391</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1037,22 +1037,22 @@
         <v>-25</v>
       </c>
       <c r="I18" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" s="14">
-        <v>-33.333333333333</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="L18" s="14">
-        <v>-40</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="M18" s="14">
-        <v>-50</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.75</v>
+        <v>-94.170403587443</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E19" s="14">
-        <v>-23.076923076923</v>
+        <v>75</v>
       </c>
       <c r="F19" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G19" s="15">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="H19" s="14">
-        <v>-12.5</v>
+        <v>11.538461538461</v>
       </c>
       <c r="I19" s="15">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J19" s="15">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K19" s="14">
-        <v>6.25</v>
+        <v>11.538461538461</v>
       </c>
       <c r="L19" s="14">
-        <v>-34.615384615384</v>
+        <v>-30.120481927710</v>
       </c>
       <c r="M19" s="14">
-        <v>10.869565217391</v>
+        <v>3.571428571428</v>
       </c>
       <c r="N19" s="14">
-        <v>-45.744680851063</v>
+        <v>-42.574257425742</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1103,38 +1103,38 @@
       <c r="C20" s="15">
         <v>4</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>300</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G20" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>400</v>
+        <v>475</v>
       </c>
       <c r="I20" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J20" s="15">
         <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="L20" s="14">
-        <v>-20</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="M20" s="14">
-        <v>38.461538461538</v>
+        <v>53.846153846153</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.534883720930</v>
+        <v>-89.361702127659</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E21" s="18">
-        <v>-5</v>
+        <v>100</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G21" s="17">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H21" s="18">
-        <v>18.333333333333</v>
+        <v>26.923076923076</v>
       </c>
       <c r="I21" s="17">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="J21" s="17">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="K21" s="18">
-        <v>21.296296296296</v>
+        <v>25.438596491228</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.815642458100</v>
+        <v>-24.338624338624</v>
       </c>
       <c r="M21" s="18">
-        <v>1.550387596899</v>
+        <v>-1.379310344827</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.417721518987</v>
+        <v>-83.657142857142</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D24" s="15">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E24" s="14">
-        <v>-38.095238095238</v>
+        <v>3.571428571428</v>
       </c>
       <c r="F24" s="15">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G24" s="15">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H24" s="14">
-        <v>-43.010752688172</v>
+        <v>-20.454545454545</v>
       </c>
       <c r="I24" s="15">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="J24" s="15">
-        <v>214</v>
+        <v>242</v>
       </c>
       <c r="K24" s="14">
-        <v>-41.121495327102</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L24" s="14">
-        <v>-46.382978723404</v>
+        <v>-37.903225806451</v>
       </c>
       <c r="M24" s="14">
-        <v>-36.363636363636</v>
+        <v>-30.941704035874</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E25" s="14">
-        <v>-55.555555555555</v>
+        <v>-25</v>
       </c>
       <c r="F25" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G25" s="15">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H25" s="14">
-        <v>-62.5</v>
+        <v>-54.761904761904</v>
       </c>
       <c r="I25" s="15">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J25" s="15">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="K25" s="14">
-        <v>-64.957264957265</v>
+        <v>-63.2</v>
       </c>
       <c r="L25" s="14">
-        <v>-72.297297297297</v>
+        <v>-70.322580645161</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D26" s="15">
         <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="F26" s="15">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G26" s="15">
         <v>24</v>
       </c>
       <c r="H26" s="14">
-        <v>37.5</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="J26" s="15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K26" s="14">
-        <v>1.666666666666</v>
+        <v>13.846153846153</v>
       </c>
       <c r="L26" s="14">
-        <v>7.017543859649</v>
+        <v>19.354838709677</v>
       </c>
       <c r="M26" s="14">
-        <v>7.017543859649</v>
+        <v>17.460317460317</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1414,8 +1414,8 @@
       <c r="K27" s="14">
         <v>-100</v>
       </c>
-      <c r="L27" s="13" t="s">
-        <v>21</v>
+      <c r="L27" s="14">
+        <v>-100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
         <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="I28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="14">
-        <v>-78.571428571428</v>
+        <v>-76.470588235294</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -908,7 +908,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -936,8 +936,8 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -946,72 +946,72 @@
         <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H16" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" s="15">
         <v>9</v>
       </c>
       <c r="K16" s="14">
-        <v>55.555555555555</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>-26.315789473684</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M16" s="14">
-        <v>-22.222222222222</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.034188034188</v>
+        <v>-87.704918032786</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="15">
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17" s="14">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="15">
         <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H17" s="14">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="I17" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J17" s="15">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K17" s="14">
-        <v>-18.181818181818</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L17" s="14">
         <v>0</v>
       </c>
       <c r="M17" s="14">
-        <v>12.5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N17" s="14">
-        <v>-64</v>
+        <v>-64.285714285714</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1028,31 +1028,31 @@
         <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="14">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18" s="14">
-        <v>-31.578947368421</v>
+        <v>-30</v>
       </c>
       <c r="L18" s="14">
-        <v>-43.478260869565</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="M18" s="14">
-        <v>-53.571428571428</v>
+        <v>-60</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.170403587443</v>
+        <v>-94.308943089430</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1063,37 +1063,37 @@
         <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>75</v>
+        <v>-30</v>
       </c>
       <c r="F19" s="15">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G19" s="15">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="H19" s="14">
-        <v>11.538461538461</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I19" s="15">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J19" s="15">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="K19" s="14">
-        <v>11.538461538461</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="L19" s="14">
-        <v>-30.120481927710</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="M19" s="14">
-        <v>3.571428571428</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="N19" s="14">
-        <v>-42.574257425742</v>
+        <v>-45.945945945945</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>4</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="E20" s="14">
+        <v>200</v>
       </c>
       <c r="F20" s="15">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G20" s="15">
         <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>475</v>
+        <v>375</v>
       </c>
       <c r="I20" s="15">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J20" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K20" s="14">
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="L20" s="14">
-        <v>-13.043478260869</v>
+        <v>-2.127659574468</v>
       </c>
       <c r="M20" s="14">
-        <v>53.846153846153</v>
+        <v>48.387096774193</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.361702127659</v>
+        <v>-88.613861386138</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>100</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="F21" s="17">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="G21" s="17">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H21" s="18">
-        <v>26.923076923076</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="J21" s="17">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="K21" s="18">
-        <v>25.438596491228</v>
+        <v>16.541353383458</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.338624338624</v>
+        <v>-23.645320197044</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.379310344827</v>
+        <v>-8.284023668639</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.657142857142</v>
+        <v>-83.632523759239</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1194,11 +1194,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
         <v>1</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D24" s="15">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E24" s="14">
-        <v>3.571428571428</v>
+        <v>105.263157894737</v>
       </c>
       <c r="F24" s="15">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="G24" s="15">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H24" s="14">
-        <v>-20.454545454545</v>
+        <v>4.347826086956</v>
       </c>
       <c r="I24" s="15">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="J24" s="15">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="K24" s="14">
-        <v>-36.363636363636</v>
+        <v>-26.436781609195</v>
       </c>
       <c r="L24" s="14">
-        <v>-37.903225806451</v>
+        <v>-28.089887640449</v>
       </c>
       <c r="M24" s="14">
-        <v>-30.941704035874</v>
+        <v>-18.297872340425</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E25" s="14">
-        <v>-25</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="15">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G25" s="15">
         <v>42</v>
       </c>
       <c r="H25" s="14">
-        <v>-54.761904761904</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I25" s="15">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J25" s="15">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="K25" s="14">
-        <v>-63.2</v>
+        <v>-64.444444444444</v>
       </c>
       <c r="L25" s="14">
-        <v>-70.322580645161</v>
+        <v>-70.552147239263</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>160</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F26" s="15">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G26" s="15">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H26" s="14">
-        <v>58.333333333333</v>
+        <v>25.925925925925</v>
       </c>
       <c r="I26" s="15">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J26" s="15">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="K26" s="14">
-        <v>13.846153846153</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L26" s="14">
-        <v>19.354838709677</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M26" s="14">
-        <v>17.460317460317</v>
+        <v>9.859154929577</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1400,7 +1400,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1428,23 +1428,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
         <v>4</v>
@@ -1499,8 +1499,8 @@
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+      <c r="M29" s="14">
+        <v>-100</v>
       </c>
       <c r="N29" s="13" t="s">
         <v>21</v>
@@ -1540,8 +1540,8 @@
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+      <c r="M30" s="14">
+        <v>-100</v>
       </c>
       <c r="N30" s="13" t="s">
         <v>21</v>
@@ -1638,7 +1638,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,41 +895,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="15">
+        <v>1</v>
       </c>
       <c r="G15" s="15">
+        <v>2</v>
+      </c>
+      <c r="H15" s="14">
+        <v>-50</v>
+      </c>
+      <c r="I15" s="15">
         <v>1</v>
       </c>
-      <c r="H15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="J15" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M15" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N15" s="14">
-        <v>-100</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,7 +937,7 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
@@ -946,31 +946,31 @@
         <v>21</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I16" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" s="15">
         <v>9</v>
       </c>
       <c r="K16" s="14">
-        <v>66.666666666666</v>
+        <v>88.888888888888</v>
       </c>
       <c r="L16" s="14">
-        <v>-28.571428571428</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M16" s="14">
-        <v>-31.818181818181</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.704918032786</v>
+        <v>-87.681159420289</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -980,38 +980,38 @@
       <c r="C17" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="15">
-        <v>6</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-66.666666666666</v>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
         <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H17" s="14">
-        <v>-50</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I17" s="15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J17" s="15">
         <v>28</v>
       </c>
       <c r="K17" s="14">
-        <v>-28.571428571428</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L17" s="14">
-        <v>0</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="M17" s="14">
-        <v>11.111111111111</v>
+        <v>15.789473684210</v>
       </c>
       <c r="N17" s="14">
-        <v>-64.285714285714</v>
+        <v>-63.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
         <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I18" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J18" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K18" s="14">
-        <v>-30</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="L18" s="14">
-        <v>-39.130434782608</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="M18" s="14">
-        <v>-60</v>
+        <v>-55.263157894736</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.308943089430</v>
+        <v>-93.656716417910</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>-30</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G19" s="15">
         <v>33</v>
       </c>
       <c r="H19" s="14">
-        <v>-18.181818181818</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="I19" s="15">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J19" s="15">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K19" s="14">
-        <v>-3.225806451612</v>
+        <v>-4.411764705882</v>
       </c>
       <c r="L19" s="14">
-        <v>-34.782608695652</v>
+        <v>-32.989690721649</v>
       </c>
       <c r="M19" s="14">
-        <v>-3.225806451612</v>
+        <v>-2.985074626865</v>
       </c>
       <c r="N19" s="14">
-        <v>-45.945945945945</v>
+        <v>-45.378151260504</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G20" s="15">
         <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>375</v>
+        <v>275</v>
       </c>
       <c r="I20" s="15">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J20" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K20" s="14">
-        <v>360</v>
+        <v>327.272727272727</v>
       </c>
       <c r="L20" s="14">
-        <v>-2.127659574468</v>
+        <v>-2.083333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>48.387096774193</v>
+        <v>42.424242424242</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.613861386138</v>
+        <v>-89.293849658314</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.526315789473</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F21" s="17">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>5.357142857142</v>
       </c>
       <c r="I21" s="17">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="J21" s="17">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="K21" s="18">
-        <v>16.541353383458</v>
+        <v>17.361111111111</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.645320197044</v>
+        <v>-20.657276995305</v>
       </c>
       <c r="M21" s="18">
-        <v>-8.284023668639</v>
+        <v>-6.111111111111</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.632523759239</v>
+        <v>-83.639883833494</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D24" s="15">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E24" s="14">
-        <v>105.263157894737</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F24" s="15">
+        <v>100</v>
+      </c>
+      <c r="G24" s="15">
         <v>96</v>
       </c>
-      <c r="G24" s="15">
-        <v>92</v>
-      </c>
       <c r="H24" s="14">
-        <v>4.347826086956</v>
+        <v>4.166666666666</v>
       </c>
       <c r="I24" s="15">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="J24" s="15">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="K24" s="14">
-        <v>-26.436781609195</v>
+        <v>-26.643598615917</v>
       </c>
       <c r="L24" s="14">
-        <v>-28.089887640449</v>
+        <v>-27.147766323024</v>
       </c>
       <c r="M24" s="14">
-        <v>-18.297872340425</v>
+        <v>-15.2</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>-80</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F25" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G25" s="15">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H25" s="14">
-        <v>-66.666666666666</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J25" s="15">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="K25" s="14">
-        <v>-64.444444444444</v>
+        <v>-63.888888888888</v>
       </c>
       <c r="L25" s="14">
-        <v>-70.552147239263</v>
+        <v>-71.270718232044</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1350,34 +1350,34 @@
         <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E26" s="14">
-        <v>-57.142857142857</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F26" s="15">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G26" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H26" s="14">
-        <v>25.925925925925</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J26" s="15">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="K26" s="14">
-        <v>8.333333333333</v>
+        <v>-2.409638554216</v>
       </c>
       <c r="L26" s="14">
-        <v>18.181818181818</v>
+        <v>12.5</v>
       </c>
       <c r="M26" s="14">
-        <v>9.859154929577</v>
+        <v>6.578947368421</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>2</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F27" s="15">
+        <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>20</v>
+        <v>-75</v>
+      </c>
+      <c r="I27" s="15">
+        <v>1</v>
       </c>
       <c r="J27" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="L27" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1447,16 +1447,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="15">
         <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>-50</v>
+        <v>-37.5</v>
       </c>
       <c r="L28" s="14">
-        <v>-76.470588235294</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,32 +1554,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="15">
+        <v>1</v>
+      </c>
+      <c r="K31" s="14">
+        <v>200</v>
+      </c>
+      <c r="L31" s="14">
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -895,14 +895,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="15">
         <v>1</v>
       </c>
       <c r="E15" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -917,13 +917,13 @@
         <v>1</v>
       </c>
       <c r="J15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>-80</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
+        <v>-83.333333333333</v>
+      </c>
+      <c r="L15" s="14">
+        <v>0</v>
       </c>
       <c r="M15" s="14">
         <v>0</v>
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
       </c>
       <c r="F16" s="15">
         <v>4</v>
       </c>
       <c r="G16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="14">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I16" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K16" s="14">
-        <v>88.888888888888</v>
+        <v>80</v>
       </c>
       <c r="L16" s="14">
-        <v>-22.727272727272</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="14">
-        <v>-22.727272727272</v>
+        <v>-28</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.681159420289</v>
+        <v>-88.157894736842</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>4</v>
+      </c>
+      <c r="D17" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="E17" s="14">
+        <v>100</v>
       </c>
       <c r="F17" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="15">
         <v>9</v>
       </c>
       <c r="H17" s="14">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I17" s="15">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J17" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K17" s="14">
-        <v>-21.428571428571</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>-4.347826086956</v>
+        <v>13.043478260869</v>
       </c>
       <c r="M17" s="14">
-        <v>15.789473684210</v>
+        <v>30</v>
       </c>
       <c r="N17" s="14">
-        <v>-63.333333333333</v>
+        <v>-59.375</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
         <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I18" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K18" s="14">
-        <v>-26.086956521739</v>
+        <v>-28</v>
       </c>
       <c r="L18" s="14">
-        <v>-26.086956521739</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="M18" s="14">
-        <v>-55.263157894736</v>
+        <v>-58.139534883720</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.656716417910</v>
+        <v>-93.835616438356</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>6</v>
+      </c>
+      <c r="D19" s="15">
         <v>5</v>
       </c>
-      <c r="D19" s="15">
-        <v>6</v>
-      </c>
       <c r="E19" s="14">
-        <v>-16.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F19" s="15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" s="15">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H19" s="14">
-        <v>-21.212121212121</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J19" s="15">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K19" s="14">
-        <v>-4.411764705882</v>
+        <v>0</v>
       </c>
       <c r="L19" s="14">
-        <v>-32.989690721649</v>
+        <v>-32.407407407407</v>
       </c>
       <c r="M19" s="14">
-        <v>-2.985074626865</v>
+        <v>-3.947368421052</v>
       </c>
       <c r="N19" s="14">
-        <v>-45.378151260504</v>
+        <v>-42.063492063492</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,10 +1101,10 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="14">
         <v>0</v>
@@ -1113,28 +1113,28 @@
         <v>15</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>275</v>
+        <v>114.285714285714</v>
       </c>
       <c r="I20" s="15">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J20" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K20" s="14">
-        <v>327.272727272727</v>
+        <v>240</v>
       </c>
       <c r="L20" s="14">
-        <v>-2.083333333333</v>
+        <v>6.25</v>
       </c>
       <c r="M20" s="14">
-        <v>42.424242424242</v>
+        <v>45.714285714285</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.293849658314</v>
+        <v>-89.484536082474</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>27.272727272727</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F21" s="17">
         <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="H21" s="18">
-        <v>5.357142857142</v>
+        <v>15.686274509803</v>
       </c>
       <c r="I21" s="17">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="J21" s="17">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="K21" s="18">
-        <v>17.361111111111</v>
+        <v>17.610062893081</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.657276995305</v>
+        <v>-17.621145374449</v>
       </c>
       <c r="M21" s="18">
-        <v>-6.111111111111</v>
+        <v>-6.5</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.639883833494</v>
+        <v>-83.421985815602</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M22" s="14">
         <v>0</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E24" s="14">
-        <v>-28.571428571428</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="F24" s="15">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G24" s="15">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H24" s="14">
-        <v>4.166666666666</v>
+        <v>7.446808510638</v>
       </c>
       <c r="I24" s="15">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="J24" s="15">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="K24" s="14">
-        <v>-26.643598615917</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L24" s="14">
-        <v>-27.147766323024</v>
+        <v>-27.508090614886</v>
       </c>
       <c r="M24" s="14">
-        <v>-15.2</v>
+        <v>-16.417910447761</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
         <v>9</v>
       </c>
       <c r="E25" s="14">
-        <v>-55.555555555555</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G25" s="15">
         <v>36</v>
       </c>
       <c r="H25" s="14">
-        <v>-58.333333333333</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="I25" s="15">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J25" s="15">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="K25" s="14">
-        <v>-63.888888888888</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="L25" s="14">
-        <v>-71.270718232044</v>
+        <v>-71.578947368421</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D26" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>-72.727272727272</v>
+        <v>25</v>
       </c>
       <c r="F26" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G26" s="15">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H26" s="14">
+        <v>-6.451612903225</v>
+      </c>
+      <c r="I26" s="15">
+        <v>91</v>
+      </c>
+      <c r="J26" s="15">
+        <v>91</v>
+      </c>
+      <c r="K26" s="14">
         <v>0</v>
       </c>
-      <c r="I26" s="15">
-        <v>81</v>
-      </c>
-      <c r="J26" s="15">
-        <v>83</v>
-      </c>
-      <c r="K26" s="14">
-        <v>-2.409638554216</v>
-      </c>
       <c r="L26" s="14">
-        <v>12.5</v>
+        <v>21.333333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>6.578947368421</v>
+        <v>7.058823529411</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="15">
         <v>1</v>
       </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
       <c r="E27" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
       </c>
       <c r="G27" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="15">
         <v>1</v>
       </c>
       <c r="J27" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="14">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,8 +1428,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1441,10 +1441,10 @@
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
         <v>5</v>
@@ -1502,8 +1502,8 @@
       <c r="M29" s="14">
         <v>-100</v>
       </c>
-      <c r="N29" s="13" t="s">
-        <v>21</v>
+      <c r="N29" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1543,8 +1543,8 @@
       <c r="M30" s="14">
         <v>-100</v>
       </c>
-      <c r="N30" s="13" t="s">
-        <v>21</v>
+      <c r="N30" s="14">
+        <v>-100</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -898,11 +898,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="14">
         <v>-87.5</v>
@@ -936,14 +936,14 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
-      </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>0</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="15">
         <v>4</v>
@@ -967,10 +967,10 @@
         <v>-25</v>
       </c>
       <c r="M16" s="14">
-        <v>-28</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.157894736842</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F17" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G17" s="15">
         <v>9</v>
       </c>
       <c r="H17" s="14">
-        <v>-11.111111111111</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I17" s="15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J17" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K17" s="14">
-        <v>-13.333333333333</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="L17" s="14">
-        <v>13.043478260869</v>
+        <v>12</v>
       </c>
       <c r="M17" s="14">
-        <v>30</v>
+        <v>27.272727272727</v>
       </c>
       <c r="N17" s="14">
-        <v>-59.375</v>
+        <v>-60.563380281690</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
         <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H18" s="14">
-        <v>-14.285714285714</v>
+        <v>-37.5</v>
       </c>
       <c r="I18" s="15">
         <v>18</v>
       </c>
       <c r="J18" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K18" s="14">
-        <v>-28</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L18" s="14">
-        <v>-21.739130434782</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="M18" s="14">
-        <v>-58.139534883720</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="N18" s="14">
-        <v>-93.835616438356</v>
+        <v>-94.174757281553</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>20</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F19" s="15">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G19" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I19" s="15">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J19" s="15">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="K19" s="14">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L19" s="14">
-        <v>-32.407407407407</v>
+        <v>-35.042735042735</v>
       </c>
       <c r="M19" s="14">
-        <v>-3.947368421052</v>
+        <v>-5</v>
       </c>
       <c r="N19" s="14">
-        <v>-42.063492063492</v>
+        <v>-41.984732824427</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
         <v>0</v>
       </c>
       <c r="F20" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G20" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H20" s="14">
-        <v>114.285714285714</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I20" s="15">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J20" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K20" s="14">
-        <v>240</v>
+        <v>211.764705882353</v>
       </c>
       <c r="L20" s="14">
-        <v>6.25</v>
+        <v>-5.357142857142</v>
       </c>
       <c r="M20" s="14">
-        <v>45.714285714285</v>
+        <v>32.5</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.484536082474</v>
+        <v>-89.827255278310</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>6.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G21" s="17">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H21" s="18">
-        <v>15.686274509803</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I21" s="17">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="J21" s="17">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="K21" s="18">
-        <v>17.610062893081</v>
+        <v>13.450292397660</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.621145374449</v>
+        <v>-23.015873015873</v>
       </c>
       <c r="M21" s="18">
-        <v>-6.5</v>
+        <v>-9.345794392523</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.421985815602</v>
+        <v>-83.873649210307</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,29 +1185,29 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="15">
+        <v>1</v>
+      </c>
+      <c r="H22" s="14">
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>1</v>
       </c>
       <c r="J22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="14">
         <v>-80</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E24" s="14">
-        <v>-5.263157894736</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="G24" s="15">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="H24" s="14">
-        <v>7.446808510638</v>
+        <v>1.282051282051</v>
       </c>
       <c r="I24" s="15">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="J24" s="15">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="K24" s="14">
-        <v>-27.272727272727</v>
+        <v>-27.8125</v>
       </c>
       <c r="L24" s="14">
-        <v>-27.508090614886</v>
+        <v>-34.188034188034</v>
       </c>
       <c r="M24" s="14">
-        <v>-16.417910447761</v>
+        <v>-20.344827586206</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25" s="14">
-        <v>-66.666666666666</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F25" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G25" s="15">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H25" s="14">
-        <v>-61.111111111111</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I25" s="15">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J25" s="15">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="K25" s="14">
-        <v>-64.705882352941</v>
+        <v>-65.625</v>
       </c>
       <c r="L25" s="14">
-        <v>-71.578947368421</v>
+        <v>-74.885844748858</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G26" s="15">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H26" s="14">
-        <v>-6.451612903225</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="I26" s="15">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="J26" s="15">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="K26" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="14">
-        <v>21.333333333333</v>
+        <v>24.691358024691</v>
       </c>
       <c r="M26" s="14">
-        <v>7.058823529411</v>
+        <v>8.602150537634</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,11 +1390,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>3</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="15">
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K28" s="14">
-        <v>-37.5</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L28" s="14">
-        <v>-70.588235294117</v>
+        <v>-64.705882352941</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1579,7 +1579,7 @@
         <v>200</v>
       </c>
       <c r="L31" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -881,8 +881,8 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="14">
+        <v>-100</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N15" s="14">
         <v>-87.5</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="15">
+        <v>3</v>
+      </c>
+      <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="14">
+        <v>50</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G16" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" s="14">
-        <v>300</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I16" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J16" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K16" s="14">
-        <v>80</v>
+        <v>83.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-25</v>
+        <v>-12</v>
       </c>
       <c r="M16" s="14">
-        <v>-30.769230769230</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.888888888888</v>
+        <v>-87.356321839080</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,81 +978,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E17" s="14">
-        <v>200</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H17" s="14">
-        <v>11.111111111111</v>
+        <v>-25</v>
       </c>
       <c r="I17" s="15">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J17" s="15">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="K17" s="14">
-        <v>-9.677419354838</v>
+        <v>-27.5</v>
       </c>
       <c r="L17" s="14">
-        <v>12</v>
+        <v>11.538461538461</v>
       </c>
       <c r="M17" s="14">
-        <v>27.272727272727</v>
+        <v>20.833333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>-60.563380281690</v>
+        <v>-62.820512820512</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>9</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>125</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H18" s="14">
-        <v>-37.5</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I18" s="15">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J18" s="15">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K18" s="14">
-        <v>-33.333333333333</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="L18" s="14">
-        <v>-37.931034482758</v>
+        <v>-15.625</v>
       </c>
       <c r="M18" s="14">
-        <v>-59.090909090909</v>
+        <v>-50.909090909090</v>
       </c>
       <c r="N18" s="14">
-        <v>-94.174757281553</v>
+        <v>-91.916167664670</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1063,37 +1063,37 @@
         <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>-57.142857142857</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G19" s="15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H19" s="14">
-        <v>-25</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="I19" s="15">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J19" s="15">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K19" s="14">
-        <v>-5</v>
+        <v>-11.235955056179</v>
       </c>
       <c r="L19" s="14">
-        <v>-35.042735042735</v>
+        <v>-36.8</v>
       </c>
       <c r="M19" s="14">
-        <v>-5</v>
+        <v>-7.058823529411</v>
       </c>
       <c r="N19" s="14">
-        <v>-41.984732824427</v>
+        <v>-42.335766423357</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="15">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H20" s="14">
-        <v>44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="15">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J20" s="15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K20" s="14">
-        <v>211.764705882353</v>
+        <v>145.454545454545</v>
       </c>
       <c r="L20" s="14">
-        <v>-5.357142857142</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M20" s="14">
-        <v>32.5</v>
+        <v>14.893617021276</v>
       </c>
       <c r="N20" s="14">
-        <v>-89.827255278310</v>
+        <v>-90.425531914893</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="F21" s="17">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G21" s="17">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.263157894736</v>
+        <v>-17.910447761194</v>
       </c>
       <c r="I21" s="17">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="J21" s="17">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="K21" s="18">
-        <v>13.450292397660</v>
+        <v>6</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.015873015873</v>
+        <v>-20.599250936329</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.345794392523</v>
+        <v>-11.666666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.873649210307</v>
+        <v>-83.641975308642</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1185,11 +1185,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" s="15">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E24" s="14">
-        <v>8.333333333333</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="F24" s="15">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="G24" s="15">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H24" s="14">
-        <v>1.282051282051</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I24" s="15">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="J24" s="15">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="K24" s="14">
-        <v>-27.8125</v>
+        <v>-29.768786127167</v>
       </c>
       <c r="L24" s="14">
-        <v>-34.188034188034</v>
+        <v>-35.543766578249</v>
       </c>
       <c r="M24" s="14">
-        <v>-20.344827586206</v>
+        <v>-22.611464968152</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E25" s="14">
-        <v>-85.714285714285</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F25" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="15">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H25" s="14">
-        <v>-71.428571428571</v>
+        <v>-69.444444444444</v>
       </c>
       <c r="I25" s="15">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J25" s="15">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="K25" s="14">
-        <v>-65.625</v>
+        <v>-66.081871345029</v>
       </c>
       <c r="L25" s="14">
-        <v>-74.885844748858</v>
+        <v>-75.319148936170</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D26" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F26" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G26" s="15">
         <v>35</v>
       </c>
       <c r="H26" s="14">
-        <v>-25.714285714285</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="I26" s="15">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J26" s="15">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K26" s="14">
-        <v>1</v>
+        <v>-1.869158878504</v>
       </c>
       <c r="L26" s="14">
-        <v>24.691358024691</v>
+        <v>20.689655172413</v>
       </c>
       <c r="M26" s="14">
-        <v>8.602150537634</v>
+        <v>1.941747572815</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>3</v>
-      </c>
       <c r="E28" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="15">
         <v>6</v>
       </c>
       <c r="J28" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" s="14">
-        <v>-45.454545454545</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="14">
         <v>-64.705882352941</v>

--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -884,8 +884,8 @@
       <c r="L14" s="14">
         <v>-100</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="14">
+        <v>-100</v>
       </c>
       <c r="N14" s="14">
         <v>-100</v>
@@ -898,29 +898,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
+      <c r="D15" s="15">
         <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>1</v>
       </c>
       <c r="J15" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="L15" s="14">
         <v>0</v>
@@ -929,48 +929,48 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N15" s="14">
-        <v>-87.5</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>3</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="14">
-        <v>133.333333333333</v>
+        <v>25</v>
       </c>
       <c r="I16" s="15">
         <v>22</v>
       </c>
       <c r="J16" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K16" s="14">
-        <v>83.333333333333</v>
+        <v>69.230769230769</v>
       </c>
       <c r="L16" s="14">
-        <v>-12</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M16" s="14">
         <v>-15.384615384615</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.356321839080</v>
+        <v>-88.108108108108</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-77.777777777777</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H17" s="14">
-        <v>-25</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="I17" s="15">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J17" s="15">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K17" s="14">
-        <v>-27.5</v>
+        <v>-28.888888888888</v>
       </c>
       <c r="L17" s="14">
-        <v>11.538461538461</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M17" s="14">
-        <v>20.833333333333</v>
+        <v>28</v>
       </c>
       <c r="N17" s="14">
-        <v>-62.820512820512</v>
+        <v>-59.493670886075</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>9</v>
-      </c>
-      <c r="D18" s="15">
-        <v>4</v>
-      </c>
-      <c r="E18" s="14">
-        <v>125</v>
+        <v>2</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
         <v>13</v>
       </c>
       <c r="G18" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H18" s="14">
-        <v>18.181818181818</v>
+        <v>62.5</v>
       </c>
       <c r="I18" s="15">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J18" s="15">
         <v>31</v>
       </c>
       <c r="K18" s="14">
-        <v>-12.903225806451</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>-15.625</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="M18" s="14">
-        <v>-50.909090909090</v>
+        <v>-52.307692307692</v>
       </c>
       <c r="N18" s="14">
-        <v>-91.916167664670</v>
+        <v>-91.193181818181</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>-66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F19" s="15">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G19" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H19" s="14">
-        <v>-37.037037037037</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I19" s="15">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J19" s="15">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="K19" s="14">
-        <v>-11.235955056179</v>
+        <v>-6.25</v>
       </c>
       <c r="L19" s="14">
-        <v>-36.8</v>
+        <v>-32.835820895522</v>
       </c>
       <c r="M19" s="14">
-        <v>-7.058823529411</v>
+        <v>0</v>
       </c>
       <c r="N19" s="14">
-        <v>-42.335766423357</v>
+        <v>-38.356164383561</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
         <v>5</v>
       </c>
       <c r="E20" s="14">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G20" s="15">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H20" s="14">
-        <v>-33.333333333333</v>
+        <v>-43.75</v>
       </c>
       <c r="I20" s="15">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J20" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K20" s="14">
-        <v>145.454545454545</v>
+        <v>107.407407407407</v>
       </c>
       <c r="L20" s="14">
-        <v>-5.263157894736</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="M20" s="14">
-        <v>14.893617021276</v>
+        <v>9.803921568627</v>
       </c>
       <c r="N20" s="14">
-        <v>-90.425531914893</v>
+        <v>-90.743801652892</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-37.931034482758</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="F21" s="17">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>-17.910447761194</v>
+        <v>-21.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="J21" s="17">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="K21" s="18">
-        <v>6</v>
+        <v>5.936073059360</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.599250936329</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.666666666666</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.641975308642</v>
+        <v>-83.164005805515</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E24" s="14">
-        <v>-53.846153846153</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="F24" s="15">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G24" s="15">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H24" s="14">
-        <v>-35.294117647058</v>
+        <v>-32.911392405063</v>
       </c>
       <c r="I24" s="15">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="J24" s="15">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="K24" s="14">
-        <v>-29.768786127167</v>
+        <v>-30.163043478260</v>
       </c>
       <c r="L24" s="14">
-        <v>-35.543766578249</v>
+        <v>-35.910224438902</v>
       </c>
       <c r="M24" s="14">
-        <v>-22.611464968152</v>
+        <v>-23.738872403560</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E25" s="14">
-        <v>-72.727272727272</v>
+        <v>-93.333333333333</v>
       </c>
       <c r="F25" s="15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G25" s="15">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H25" s="14">
-        <v>-69.444444444444</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I25" s="15">
         <v>58</v>
       </c>
       <c r="J25" s="15">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="K25" s="14">
-        <v>-66.081871345029</v>
+        <v>-68.817204301075</v>
       </c>
       <c r="L25" s="14">
-        <v>-75.319148936170</v>
+        <v>-76.8</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E26" s="14">
-        <v>-42.857142857142</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
+        <v>30</v>
+      </c>
+      <c r="G26" s="15">
         <v>27</v>
       </c>
-      <c r="G26" s="15">
-        <v>35</v>
-      </c>
       <c r="H26" s="14">
-        <v>-22.857142857142</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I26" s="15">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J26" s="15">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K26" s="14">
-        <v>-1.869158878504</v>
+        <v>0.909090909090</v>
       </c>
       <c r="L26" s="14">
-        <v>20.689655172413</v>
+        <v>20.652173913043</v>
       </c>
       <c r="M26" s="14">
-        <v>1.941747572815</v>
+        <v>2.777777777777</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1390,29 +1390,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="D27" s="15">
         <v>1</v>
       </c>
+      <c r="E27" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
         <v>1</v>
       </c>
       <c r="J27" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="14">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="L27" s="14">
         <v>-50</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>1</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="15">
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="14">
-        <v>-50</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L28" s="14">
-        <v>-64.705882352941</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1563,11 +1563,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>

--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -895,55 +895,55 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="15">
         <v>1</v>
       </c>
-      <c r="E15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
+        <v>1</v>
       </c>
       <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
+      </c>
+      <c r="I15" s="15">
         <v>2</v>
-      </c>
-      <c r="H15" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I15" s="15">
-        <v>1</v>
       </c>
       <c r="J15" s="15">
         <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>-85.714285714285</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>-90</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
         <v>5</v>
@@ -955,22 +955,22 @@
         <v>25</v>
       </c>
       <c r="I16" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J16" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="14">
-        <v>69.230769230769</v>
+        <v>64.285714285714</v>
       </c>
       <c r="L16" s="14">
-        <v>-15.384615384615</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="M16" s="14">
-        <v>-15.384615384615</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.108108108108</v>
+        <v>-88.144329896907</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E17" s="14">
-        <v>-40</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="15">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="H17" s="14">
-        <v>-41.176470588235</v>
+        <v>-62.5</v>
       </c>
       <c r="I17" s="15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J17" s="15">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="K17" s="14">
-        <v>-28.888888888888</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="L17" s="14">
-        <v>23.076923076923</v>
+        <v>13.333333333333</v>
       </c>
       <c r="M17" s="14">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="N17" s="14">
-        <v>-59.493670886075</v>
+        <v>-57.5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1021,38 +1021,38 @@
       <c r="C18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="15">
+        <v>2</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="15">
         <v>8</v>
       </c>
       <c r="H18" s="14">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="I18" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J18" s="15">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K18" s="14">
         <v>0</v>
       </c>
       <c r="L18" s="14">
-        <v>-8.823529411764</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="M18" s="14">
-        <v>-52.307692307692</v>
+        <v>-54.794520547945</v>
       </c>
       <c r="N18" s="14">
-        <v>-91.193181818181</v>
+        <v>-91.152815013404</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19" s="14">
-        <v>42.857142857142</v>
+        <v>60</v>
       </c>
       <c r="F19" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G19" s="15">
         <v>28</v>
       </c>
       <c r="H19" s="14">
-        <v>-21.428571428571</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I19" s="15">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="J19" s="15">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K19" s="14">
-        <v>-6.25</v>
+        <v>-1.980198019801</v>
       </c>
       <c r="L19" s="14">
-        <v>-32.835820895522</v>
+        <v>-29.787234042553</v>
       </c>
       <c r="M19" s="14">
-        <v>0</v>
+        <v>3.125</v>
       </c>
       <c r="N19" s="14">
-        <v>-38.356164383561</v>
+        <v>-34.868421052631</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>5</v>
+      </c>
+      <c r="D20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="15">
-        <v>5</v>
-      </c>
       <c r="E20" s="14">
-        <v>-60</v>
+        <v>150</v>
       </c>
       <c r="F20" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H20" s="14">
-        <v>-43.75</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I20" s="15">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J20" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K20" s="14">
-        <v>107.407407407407</v>
+        <v>110.344827586207</v>
       </c>
       <c r="L20" s="14">
-        <v>-3.448275862068</v>
+        <v>5.172413793103</v>
       </c>
       <c r="M20" s="14">
-        <v>9.803921568627</v>
+        <v>12.962962962963</v>
       </c>
       <c r="N20" s="14">
-        <v>-90.743801652892</v>
+        <v>-90.542635658914</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
         <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.526315789473</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.333333333333</v>
+        <v>-20.253164556962</v>
       </c>
       <c r="I21" s="17">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="J21" s="17">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="K21" s="18">
-        <v>5.936073059360</v>
+        <v>5.882352941176</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.142857142857</v>
+        <v>-13.993174061433</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.111111111111</v>
+        <v>-10.320284697508</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.164005805515</v>
+        <v>-82.680412371134</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1213,7 +1213,7 @@
         <v>-80</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D24" s="15">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E24" s="14">
-        <v>-27.272727272727</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="F24" s="15">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G24" s="15">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H24" s="14">
-        <v>-32.911392405063</v>
+        <v>-30.864197530864</v>
       </c>
       <c r="I24" s="15">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="J24" s="15">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="K24" s="14">
-        <v>-30.163043478260</v>
+        <v>-29.820051413881</v>
       </c>
       <c r="L24" s="14">
-        <v>-35.910224438902</v>
+        <v>-35.915492957746</v>
       </c>
       <c r="M24" s="14">
-        <v>-23.738872403560</v>
+        <v>-25</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D25" s="15">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E25" s="14">
-        <v>-93.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G25" s="15">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H25" s="14">
-        <v>-83.333333333333</v>
+        <v>-74.358974358974</v>
       </c>
       <c r="I25" s="15">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J25" s="15">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="K25" s="14">
-        <v>-68.817204301075</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L25" s="14">
-        <v>-76.8</v>
+        <v>-76.029962546816</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G26" s="15">
         <v>27</v>
       </c>
       <c r="H26" s="14">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="I26" s="15">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J26" s="15">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="K26" s="14">
-        <v>0.909090909090</v>
+        <v>0.847457627118</v>
       </c>
       <c r="L26" s="14">
-        <v>20.652173913043</v>
+        <v>23.958333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>2.777777777777</v>
+        <v>2.586206896551</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,35 +1387,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="15">
+      <c r="C27" s="15">
         <v>1</v>
       </c>
-      <c r="E27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
+        <v>1</v>
       </c>
       <c r="G27" s="15">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14">
+        <v>0</v>
+      </c>
+      <c r="I27" s="15">
         <v>2</v>
-      </c>
-      <c r="H27" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="15">
-        <v>1</v>
       </c>
       <c r="J27" s="15">
         <v>9</v>
       </c>
       <c r="K27" s="14">
-        <v>-88.888888888888</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="L27" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
         <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="15">
         <v>7</v>
       </c>
       <c r="J28" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="14">
-        <v>-46.153846153846</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="14">
         <v>-61.111111111111</v>

--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -905,31 +905,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="15">
         <v>7</v>
       </c>
       <c r="K15" s="14">
-        <v>-71.428571428571</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L15" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M15" s="14">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="N15" s="14">
-        <v>-80</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,40 +937,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
+        <v>6</v>
+      </c>
+      <c r="G16" s="15">
         <v>5</v>
       </c>
-      <c r="G16" s="15">
-        <v>4</v>
-      </c>
       <c r="H16" s="14">
+        <v>20</v>
+      </c>
+      <c r="I16" s="15">
         <v>25</v>
       </c>
-      <c r="I16" s="15">
-        <v>23</v>
-      </c>
       <c r="J16" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="14">
-        <v>64.285714285714</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>-14.814814814814</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="M16" s="14">
-        <v>-20.689655172413</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.144329896907</v>
+        <v>-87.922705314009</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,40 +978,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-77.777777777777</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17" s="15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H17" s="14">
-        <v>-62.5</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I17" s="15">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J17" s="15">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K17" s="14">
-        <v>-37.037037037037</v>
+        <v>-37.288135593220</v>
       </c>
       <c r="L17" s="14">
-        <v>13.333333333333</v>
+        <v>5.714285714285</v>
       </c>
       <c r="M17" s="14">
-        <v>36</v>
+        <v>37.037037037037</v>
       </c>
       <c r="N17" s="14">
-        <v>-57.5</v>
+        <v>-55.952380952380</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,40 +1019,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
         <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>75</v>
+        <v>114.285714285714</v>
       </c>
       <c r="I18" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J18" s="15">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K18" s="14">
-        <v>0</v>
+        <v>2.941176470588</v>
       </c>
       <c r="L18" s="14">
-        <v>-5.714285714285</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="M18" s="14">
-        <v>-54.794520547945</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="N18" s="14">
-        <v>-91.152815013404</v>
+        <v>-91.094147582697</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F19" s="15">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G19" s="15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H19" s="14">
-        <v>-14.285714285714</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I19" s="15">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="J19" s="15">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K19" s="14">
-        <v>-1.980198019801</v>
+        <v>2.803738317757</v>
       </c>
       <c r="L19" s="14">
-        <v>-29.787234042553</v>
+        <v>-23.611111111111</v>
       </c>
       <c r="M19" s="14">
-        <v>3.125</v>
+        <v>7.843137254901</v>
       </c>
       <c r="N19" s="14">
-        <v>-34.868421052631</v>
+        <v>-31.25</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
         <v>5</v>
       </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
       <c r="E20" s="14">
-        <v>150</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H20" s="14">
-        <v>-28.571428571428</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I20" s="15">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J20" s="15">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K20" s="14">
-        <v>110.344827586207</v>
+        <v>82.352941176470</v>
       </c>
       <c r="L20" s="14">
-        <v>5.172413793103</v>
+        <v>5.084745762711</v>
       </c>
       <c r="M20" s="14">
-        <v>12.962962962963</v>
+        <v>6.896551724137</v>
       </c>
       <c r="N20" s="14">
-        <v>-90.542635658914</v>
+        <v>-90.841949778434</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.253164556962</v>
+        <v>-15.294117647058</v>
       </c>
       <c r="I21" s="17">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="J21" s="17">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="K21" s="18">
-        <v>5.882352941176</v>
+        <v>6.25</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.993174061433</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M21" s="18">
-        <v>-10.320284697508</v>
+        <v>-9.030100334448</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.680412371134</v>
+        <v>-82.245430809399</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1194,11 +1194,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
         <v>1</v>
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D24" s="15">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>-19.047619047619</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="15">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G24" s="15">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H24" s="14">
-        <v>-30.864197530864</v>
+        <v>-34.408602150537</v>
       </c>
       <c r="I24" s="15">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="J24" s="15">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="K24" s="14">
-        <v>-29.820051413881</v>
+        <v>-30.024213075060</v>
       </c>
       <c r="L24" s="14">
-        <v>-35.915492957746</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="M24" s="14">
-        <v>-25</v>
+        <v>-26.463104325699</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25" s="15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F25" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G25" s="15">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H25" s="14">
-        <v>-74.358974358974</v>
+        <v>-68.181818181818</v>
       </c>
       <c r="I25" s="15">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J25" s="15">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="K25" s="14">
-        <v>-66.666666666666</v>
+        <v>-66.176470588235</v>
       </c>
       <c r="L25" s="14">
-        <v>-76.029962546816</v>
+        <v>-76.206896551724</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F26" s="15">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G26" s="15">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H26" s="14">
-        <v>0</v>
+        <v>34.782608695652</v>
       </c>
       <c r="I26" s="15">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="J26" s="15">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K26" s="14">
-        <v>0.847457627118</v>
+        <v>7.317073170731</v>
       </c>
       <c r="L26" s="14">
-        <v>23.958333333333</v>
+        <v>29.411764705882</v>
       </c>
       <c r="M26" s="14">
-        <v>2.586206896551</v>
+        <v>10.924369747899</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,25 +1397,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
         <v>9</v>
       </c>
       <c r="K27" s="14">
-        <v>-77.777777777777</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,25 +1438,25 @@
         <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I28" s="15">
         <v>7</v>
       </c>
       <c r="J28" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="14">
-        <v>-50</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>-61.111111111111</v>
+        <v>-65</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,29 +1554,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>2</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>2</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>
       </c>
       <c r="J31" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K31" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L31" s="14">
         <v>50</v>

--- a/data/source/weekly/cs-en-us-068pct.xlsx
+++ b/data/source/weekly/cs-en-us-068pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -895,8 +895,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -923,7 +923,7 @@
         <v>-57.142857142857</v>
       </c>
       <c r="L15" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M15" s="14">
         <v>-25</v>
@@ -936,41 +936,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
+        <v>3</v>
+      </c>
+      <c r="G16" s="15">
         <v>6</v>
       </c>
-      <c r="G16" s="15">
-        <v>5</v>
-      </c>
       <c r="H16" s="14">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="15">
         <v>25</v>
       </c>
       <c r="J16" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K16" s="14">
-        <v>66.666666666666</v>
+        <v>38.888888888888</v>
       </c>
       <c r="L16" s="14">
-        <v>-7.407407407407</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M16" s="14">
-        <v>-16.666666666666</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="N16" s="14">
-        <v>-87.922705314009</v>
+        <v>-88.532110091743</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -981,78 +981,78 @@
         <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-40</v>
+        <v>200</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" s="15">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H17" s="14">
-        <v>-64.285714285714</v>
+        <v>-45</v>
       </c>
       <c r="I17" s="15">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J17" s="15">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K17" s="14">
-        <v>-37.288135593220</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L17" s="14">
-        <v>5.714285714285</v>
+        <v>2.564102564102</v>
       </c>
       <c r="M17" s="14">
-        <v>37.037037037037</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N17" s="14">
-        <v>-55.952380952380</v>
+        <v>-54.545454545454</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="14">
-        <v>114.285714285714</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="15">
         <v>35</v>
       </c>
       <c r="J18" s="15">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K18" s="14">
-        <v>2.941176470588</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="L18" s="14">
         <v>-5.405405405405</v>
       </c>
       <c r="M18" s="14">
-        <v>-54.545454545454</v>
+        <v>-57.831325301204</v>
       </c>
       <c r="N18" s="14">
-        <v>-91.094147582697</v>
+        <v>-91.706161137440</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,40 +1060,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F19" s="15">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G19" s="15">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H19" s="14">
-        <v>11.111111111111</v>
+        <v>40</v>
       </c>
       <c r="I19" s="15">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J19" s="15">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K19" s="14">
-        <v>2.803738317757</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L19" s="14">
-        <v>-23.611111111111</v>
+        <v>-22.077922077922</v>
       </c>
       <c r="M19" s="14">
-        <v>7.843137254901</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N19" s="14">
-        <v>-31.25</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,40 +1101,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>5</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-80</v>
+        <v>4</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G20" s="15">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H20" s="14">
-        <v>-47.058823529411</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J20" s="15">
         <v>34</v>
       </c>
       <c r="K20" s="14">
-        <v>82.352941176470</v>
+        <v>94.117647058823</v>
       </c>
       <c r="L20" s="14">
-        <v>5.084745762711</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M20" s="14">
-        <v>6.896551724137</v>
+        <v>10</v>
       </c>
       <c r="N20" s="14">
-        <v>-90.841949778434</v>
+        <v>-90.846047156726</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,40 +1142,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.555555555555</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.294117647058</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="I21" s="17">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="J21" s="17">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="K21" s="18">
-        <v>6.25</v>
+        <v>7.037037037037</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.526315789473</v>
+        <v>-10.802469135802</v>
       </c>
       <c r="M21" s="18">
-        <v>-9.030100334448</v>
+        <v>-9.968847352024</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.245430809399</v>
+        <v>-82.259054634745</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D24" s="15">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>-25</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F24" s="15">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G24" s="15">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H24" s="14">
-        <v>-34.408602150537</v>
+        <v>-17.5</v>
       </c>
       <c r="I24" s="15">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="J24" s="15">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="K24" s="14">
-        <v>-30.024213075060</v>
+        <v>-28.873239436619</v>
       </c>
       <c r="L24" s="14">
-        <v>-37.037037037037</v>
+        <v>-38.289205702647</v>
       </c>
       <c r="M24" s="14">
-        <v>-26.463104325699</v>
+        <v>-28.028503562945</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,34 +1306,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D25" s="15">
+        <v>6</v>
+      </c>
+      <c r="E25" s="14">
+        <v>-83.333333333333</v>
+      </c>
+      <c r="F25" s="15">
         <v>12</v>
       </c>
-      <c r="E25" s="14">
-        <v>-58.333333333333</v>
-      </c>
-      <c r="F25" s="15">
-        <v>14</v>
-      </c>
       <c r="G25" s="15">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H25" s="14">
-        <v>-68.181818181818</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I25" s="15">
         <v>69</v>
       </c>
       <c r="J25" s="15">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="K25" s="14">
-        <v>-66.176470588235</v>
+        <v>-67.142857142857</v>
       </c>
       <c r="L25" s="14">
-        <v>-76.206896551724</v>
+        <v>-78.025477707006</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,37 +1347,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
         <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>160</v>
+        <v>40</v>
       </c>
       <c r="F26" s="15">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G26" s="15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H26" s="14">
-        <v>34.782608695652</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I26" s="15">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="J26" s="15">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K26" s="14">
-        <v>7.317073170731</v>
+        <v>9.375</v>
       </c>
       <c r="L26" s="14">
-        <v>29.411764705882</v>
+        <v>25</v>
       </c>
       <c r="M26" s="14">
-        <v>10.924369747899</v>
+        <v>10.236220472440</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,8 +1387,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1415,7 +1415,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L27" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,35 +1428,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="15">
         <v>15</v>
       </c>
       <c r="K28" s="14">
-        <v>-53.333333333333</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>-65</v>
+        <v>-60</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1554,11 +1554,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="15">
-        <v>2</v>
-      </c>
-      <c r="E31" s="14">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
